--- a/data/trans_orig/IP18B2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18B2-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,58%</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -3370,47 +3370,47 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6090</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>44,87%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2755</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>5464</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2755</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>463</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6317,42 +6317,42 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
+          <t>2619</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>61,41%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
           <t>2569</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>60,22%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>2569</t>
-        </is>
-      </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>451</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -7863,12 +7863,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -10240,12 +10240,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10918,12 +10918,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10988,12 +10988,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -11031,12 +11031,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11101,12 +11101,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11179,12 +11179,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -11709,12 +11709,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11724,12 +11724,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11779,12 +11779,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11794,12 +11794,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -11822,12 +11822,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11837,12 +11837,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11892,12 +11892,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -12387,12 +12387,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12457,12 +12457,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12472,12 +12472,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -13075,12 +13075,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -14996,12 +14996,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15011,12 +15011,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15066,12 +15066,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15261,12 +15261,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15276,12 +15276,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -15452,12 +15452,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15467,12 +15467,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15487,12 +15487,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15502,12 +15502,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -15522,12 +15522,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15939,12 +15939,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15954,12 +15954,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -16017,12 +16017,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16087,12 +16087,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16102,12 +16102,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -16893,12 +16893,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17330,12 +17330,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -17408,12 +17408,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -17423,12 +17423,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -17443,12 +17443,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -17458,12 +17458,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -17673,12 +17673,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -17688,12 +17688,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17864,12 +17864,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17879,12 +17879,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17899,12 +17899,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17914,12 +17914,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -18394,12 +18394,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -18409,12 +18409,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -18464,12 +18464,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -18479,12 +18479,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -19112,7 +19112,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -19235,12 +19235,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -19270,12 +19270,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -19840,7 +19840,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -20015,12 +20015,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -20050,12 +20050,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -20065,12 +20065,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -20211,7 +20211,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -20241,12 +20241,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -20256,12 +20256,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -20276,12 +20276,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -20291,12 +20291,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -20786,12 +20786,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -20806,12 +20806,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -20821,12 +20821,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -20841,12 +20841,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -20856,12 +20856,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -21519,12 +21519,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -22162,12 +22162,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -22177,12 +22177,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -22197,12 +22197,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -22212,12 +22212,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -22357,12 +22357,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -22372,12 +22372,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -22392,12 +22392,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -22407,12 +22407,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -22442,12 +22442,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -22510,7 +22510,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -22545,7 +22545,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -22583,12 +22583,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -22598,12 +22598,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -22618,12 +22618,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -22653,12 +22653,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -22668,12 +22668,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -22786,7 +22786,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -23035,12 +23035,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -23050,12 +23050,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -23105,12 +23105,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -23148,12 +23148,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -23163,12 +23163,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -23183,12 +23183,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -23198,12 +23198,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -23233,12 +23233,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -23301,7 +23301,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -23379,7 +23379,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -23449,7 +23449,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -23826,12 +23826,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -23841,12 +23841,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -23896,12 +23896,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -23911,12 +23911,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -23939,12 +23939,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -23954,12 +23954,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -23974,12 +23974,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -23989,12 +23989,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -24024,12 +24024,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -24205,7 +24205,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -24353,7 +24353,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -24391,12 +24391,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -24406,12 +24406,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -24431,7 +24431,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -24461,12 +24461,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -24476,12 +24476,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -24504,12 +24504,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -24519,12 +24519,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -24539,12 +24539,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -24554,12 +24554,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -25232,7 +25232,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -25262,12 +25262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -25277,12 +25277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -25458,7 +25458,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -25714,12 +25714,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -25729,12 +25729,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -25812,7 +25812,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -25832,7 +25832,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -25847,7 +25847,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -26440,7 +26440,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -26455,7 +26455,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -26588,7 +26588,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -26603,7 +26603,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -26977,7 +26977,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -27118,7 +27118,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -27148,12 +27148,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -27163,12 +27163,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -27183,12 +27183,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -27198,12 +27198,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>57,08%</t>
         </is>
       </c>
     </row>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -27383,7 +27383,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -27413,12 +27413,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -27428,12 +27428,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -27531,7 +27531,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -27569,12 +27569,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -27584,12 +27584,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -27639,12 +27639,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -27654,12 +27654,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -27913,7 +27913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -28096,7 +28096,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -28111,7 +28111,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -28282,12 +28282,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -28297,12 +28297,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -28317,12 +28317,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -28332,12 +28332,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -28380,7 +28380,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -28430,12 +28430,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -28980,7 +28980,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -29241,7 +29241,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -29269,7 +29269,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -29354,7 +29354,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -29382,7 +29382,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -29452,7 +29452,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -29490,12 +29490,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -29505,12 +29505,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -29560,12 +29560,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -29575,12 +29575,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -29775,7 +29775,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -29790,12 +29790,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -29805,12 +29805,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -29946,12 +29946,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -29961,12 +29961,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -29981,12 +29981,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -29996,12 +29996,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -30016,12 +30016,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -30031,12 +30031,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -30531,7 +30531,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -30551,7 +30551,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -30581,12 +30581,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -30596,12 +30596,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -31194,7 +31194,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -31279,7 +31279,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -31302,12 +31302,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -31317,12 +31317,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -31372,12 +31372,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -31387,12 +31387,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -31568,7 +31568,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -31583,7 +31583,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -31681,7 +31681,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -31731,7 +31731,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -31887,7 +31887,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -31937,12 +31937,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -31952,12 +31952,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -32137,7 +32137,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -32152,7 +32152,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -32167,12 +32167,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -32182,12 +32182,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -32328,7 +32328,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -32343,7 +32343,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -32358,12 +32358,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -32373,12 +32373,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -32393,12 +32393,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -32408,12 +32408,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -32589,7 +32589,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -32624,7 +32624,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -32795,7 +32795,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -32815,7 +32815,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -32865,7 +32865,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -32943,7 +32943,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -32963,7 +32963,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -33076,7 +33076,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -33606,7 +33606,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -33621,7 +33621,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -33656,7 +33656,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -33714,12 +33714,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -33729,12 +33729,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -33749,12 +33749,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -33764,12 +33764,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -33910,7 +33910,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -34279,12 +34279,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -34294,12 +34294,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -34329,12 +34329,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -34474,12 +34474,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -34489,12 +34489,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -34509,12 +34509,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -34524,12 +34524,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -34544,12 +34544,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -34559,12 +34559,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -34627,7 +34627,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -34642,7 +34642,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -34662,7 +34662,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -34677,7 +34677,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -34700,12 +34700,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -34715,12 +34715,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -34735,12 +34735,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -34750,12 +34750,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -34770,12 +34770,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -34785,12 +34785,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -34931,7 +34931,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -34981,7 +34981,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -35044,7 +35044,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -35079,7 +35079,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -35109,12 +35109,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -35124,12 +35124,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -35152,12 +35152,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -35167,12 +35167,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -35222,12 +35222,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -35237,12 +35237,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -35285,7 +35285,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -35300,12 +35300,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -35315,12 +35315,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -35335,12 +35335,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -35350,12 +35350,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -35413,12 +35413,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -35428,12 +35428,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -35448,12 +35448,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -35463,12 +35463,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -35561,12 +35561,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -35576,12 +35576,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -35943,12 +35943,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -35958,12 +35958,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -35983,7 +35983,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -36013,12 +36013,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -36028,12 +36028,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -36056,12 +36056,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -36071,12 +36071,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -36091,12 +36091,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -36106,12 +36106,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -36126,12 +36126,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -36141,12 +36141,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -36287,7 +36287,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -36372,7 +36372,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -36395,12 +36395,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -36410,12 +36410,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -36435,7 +36435,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -36465,12 +36465,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -36480,12 +36480,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -36513,7 +36513,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -36598,7 +36598,7 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -36621,12 +36621,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -36636,12 +36636,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -36656,12 +36656,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -36671,12 +36671,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -36691,12 +36691,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -36706,12 +36706,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
